--- a/isms-core-framework/A.8-technological-controls/isms-a.8.8-vulnerability-management/WKBK/90_workbooks/ISMS-IMP-A.8.8.4_TI_Indicators_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.8-vulnerability-management/WKBK/90_workbooks/ISMS-IMP-A.8.8.4_TI_Indicators_20260208.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-08 11:50:10</t>
+          <t>2026-02-08 12:26:37</t>
         </is>
       </c>
     </row>
